--- a/outputs/basic-processing/dupes-removed/psycinfo.xlsx
+++ b/outputs/basic-processing/dupes-removed/psycinfo.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q117"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,7 +611,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>19267</v>
+        <v>18076</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>19269</v>
+        <v>18078</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>19270</v>
+        <v>18079</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>19271</v>
+        <v>18080</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>19273</v>
+        <v>18082</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>19274</v>
+        <v>18083</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>19275</v>
+        <v>18084</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>19276</v>
+        <v>18085</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>19277</v>
+        <v>18086</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>19279</v>
+        <v>18088</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>19280</v>
+        <v>18089</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>19281</v>
+        <v>18090</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>19282</v>
+        <v>18091</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>19283</v>
+        <v>18092</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>19284</v>
+        <v>18093</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>19285</v>
+        <v>18094</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>19286</v>
+        <v>18095</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>19287</v>
+        <v>18096</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19288</v>
+        <v>18097</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19289</v>
+        <v>18098</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>19291</v>
+        <v>18100</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>19292</v>
+        <v>18101</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>19293</v>
+        <v>18102</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>19294</v>
+        <v>18103</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>19295</v>
+        <v>18104</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>19296</v>
+        <v>18105</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>19297</v>
+        <v>18106</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>19299</v>
+        <v>18108</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>19300</v>
+        <v>18109</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>19301</v>
+        <v>18110</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>19303</v>
+        <v>18112</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>19306</v>
+        <v>18115</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>19309</v>
+        <v>18118</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>19310</v>
+        <v>18119</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>19311</v>
+        <v>18120</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>19312</v>
+        <v>18121</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>19313</v>
+        <v>18122</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>19314</v>
+        <v>18123</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>19315</v>
+        <v>18124</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>19316</v>
+        <v>18125</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>19317</v>
+        <v>18126</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>19318</v>
+        <v>18127</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>19319</v>
+        <v>18128</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>19320</v>
+        <v>18129</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>19321</v>
+        <v>18130</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>19324</v>
+        <v>18133</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>19325</v>
+        <v>18134</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>19326</v>
+        <v>18135</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>19327</v>
+        <v>18136</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>19328</v>
+        <v>18137</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>19329</v>
+        <v>18138</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>19330</v>
+        <v>18139</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>19331</v>
+        <v>18140</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>19332</v>
+        <v>18141</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>19333</v>
+        <v>18142</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>19336</v>
+        <v>18145</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>19337</v>
+        <v>18146</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>19338</v>
+        <v>18147</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>19339</v>
+        <v>18148</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>19340</v>
+        <v>18149</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>19341</v>
+        <v>18150</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>19343</v>
+        <v>18152</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>19344</v>
+        <v>18153</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>19345</v>
+        <v>18154</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>19346</v>
+        <v>18155</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>19347</v>
+        <v>18156</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>19348</v>
+        <v>18157</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>19350</v>
+        <v>18159</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>19351</v>
+        <v>18160</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>19352</v>
+        <v>18161</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>19353</v>
+        <v>18162</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>19354</v>
+        <v>18163</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>19355</v>
+        <v>18164</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>19356</v>
+        <v>18165</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>19357</v>
+        <v>18166</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>19358</v>
+        <v>18167</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>19359</v>
+        <v>18168</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>19361</v>
+        <v>18170</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>19363</v>
+        <v>18172</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>19364</v>
+        <v>18173</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>19365</v>
+        <v>18174</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>19366</v>
+        <v>18175</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>19367</v>
+        <v>18176</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>19368</v>
+        <v>18177</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>19369</v>
+        <v>18178</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>19372</v>
+        <v>18181</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>19373</v>
+        <v>18182</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>19374</v>
+        <v>18183</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>19375</v>
+        <v>18184</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>19378</v>
+        <v>18187</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>19379</v>
+        <v>18188</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>19382</v>
+        <v>18191</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>19384</v>
+        <v>18193</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>19386</v>
+        <v>18195</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>19387</v>
+        <v>18196</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>19389</v>
+        <v>18198</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>19391</v>
+        <v>18200</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>19392</v>
+        <v>18201</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>19394</v>
+        <v>18203</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>19395</v>
+        <v>18204</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>19396</v>
+        <v>18205</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>19397</v>
+        <v>18206</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>19399</v>
+        <v>18208</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>19400</v>
+        <v>18209</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>19401</v>
+        <v>18210</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>19403</v>
+        <v>18212</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>19404</v>
+        <v>18213</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>19405</v>
+        <v>18214</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>19407</v>
+        <v>18216</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -8237,496 +8237,6 @@
       </c>
       <c r="Q110" t="n">
         <v>173</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>19412</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>maternalphysicalhealthsymptomsinthefirst8weekspostpartumamongprimiparousaustralianwomenreferences2015cooklin</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>maternal physical health symptoms in the first 8 weeks postpartum among primiparous australian women. [references]</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Cooklin, Amanda, R;Amir, Lisa, H;Jarman, Jennifer;Cullinane, Meabh;Donath, Susan, M</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Background: To describe prospectively the extent, onset, and persistence of maternal physical health symptoms (cesarean delivery pain, perineal pain, back pain, constipation, hemorrhoids, urinary incontinence, bowel incontinence, and fatigue) in the first 8 weeks postpartum. Methods: A prospective cohort of 229 primiparous women was recruited antenatally from a public and a private maternity hospital, Melbourne, Australia, between 2009 and 2011. Data were collected by self-report questionnaires at weeks 1, 2, 3, 4, and 8. Main outcome measures were a checklist of maternal health symptoms and a standardized assessment of fatigue symptoms. Results: Birth-related pain was common at week 1 (n = 80/88, 91% cesarean delivery pain; n = 92/125, 74% perineal pain), and still present for one in five women who had a cesarean birth (n = 17, 18%) at week 8. Back pain was reported by approximately half the sample at each study interval, with 25 percent (n = 48) reporting a later onset at week 2 or beyond. Fatigue was not relieved between 4 and 8 weeks. Conclusions: Women experience significant morbidity in the early weeks postpartum, the extent of which may have been underestimated in previous research relying on retrospective recall. Findings contribute to the growing body of evidence that supports early identification, treatment, and support for women's physical health problems in the postpartum. (PsycInfo Database Record (c) 2022 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Birth: Issues in Perinatal Care</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>10.1111/birt.12168</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>backgroundtodecribepropectivelytheextent,onet,andperitenceofmaternalphyicalhealthymptom(ceareandeliverypain,perinealpain,backpain,contipation,hemorrhoid,urinaryincontinence,bowelincontinence,andfatigue)inthefirt8weekpotpartum.methodapropectivecohortof229primiparouwomenwarecruitedantenatallyfromapublicandaprivatematernityhopital,melbourne,autralia,between2009and2011.datawerecollectedbyelfreportquetionnaireatweek1,2,3,4,and8.mainoutcomemeaurewereachecklitofmaternalhealthymptomandatandardizedaementoffatigueymptom.reultbirthrelatedpainwacommonatweek1(n=80/88,91%ceareandeliverypainn=92/125,74%perinealpain),andtillpreentforoneinfivewomenwhohadaceareanbirth(n=17,18%)atweek8.backpainwareportedbyapproximatelyhalftheampleateachtudyinterval,with25percent(n=48)reportingalateronetatweek2orbeyond.fatiguewanotrelievedbetween4and8week.concluionwomenexperienceignificantmorbidityintheearlyweekpotpartum,theextentofwhichmayhavebeenunderetimatedinprevioureearchrelyingonretropectiverecall.findingcontributetothegrowingbodyofevidencethatupportearlyidentification,treatment,andupportforwomen'phyicalhealthprobleminthepotpartum.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Cooklin</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q111" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>19415</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>identificationandpredictionofthefertilewindowusingnaturalcyclesreferences2015scherwitzl</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>identification and prediction of the fertile window using naturalcycles. [references]</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Scherwitzl, Elina, Berglund;Hirschberg, Angelica, Linden;Scherwitzl, Raoul</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Objectives: The aim of the study was to evaluate the ability of a novel web and mobile application to identify a woman's ovulation day and fertile window, in order to use it as a method of natural birth control. Methods: A retrospective study was performed on 1501 cycles of 317 women aged 18 to 39 years. Women entered their basal body temperatures, ovulation test results and date of menstruation into the application. Results: The mean delay from the first positive ovulation test to the temperature-based estimation of the ovulation day was 1.9 days; the length of the luteal phase varied on average by 1.25 days per user. Only 0.05% of non-fertile days were falsely attributed and found within the fertile window. Conclusions: The method is effective at identifying a user's ovulation day and fertile window and can therefore be used as a natural method of birth control. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>The European Journal of Contraception and Reproductive Health Care</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>10.3109/13625187.2014.988210</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>objectivetheaimofthetudywatoevaluatetheabilityofanovelwebandmobileapplicationtoidentifyawoman'ovulationdayandfertilewindow,inordertoueitaamethodofnaturalbirthcontrol.methodaretropectivetudywaperformedon1501cycleof317womenaged18to39year.womenenteredtheirbaalbodytemperature,ovulationtetreultanddateofmentruationintotheapplication.reultthemeandelayfromthefirtpoitiveovulationtettothetemperaturebaedetimationoftheovulationdaywa1.9daythelengthofthelutealphaevariedonaverageby1.25dayperuer.only0.05%ofnonfertiledaywerefalelyattributedandfoundwithinthefertilewindow.concluionthemethodieffectiveatidentifyingauer'ovulationdayandfertilewindowandcanthereforebeuedaanaturalmethodofbirthcontrol.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Scherwitzl</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>19416</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>pregnancycomplicationsassociatedwiththecoprevalenceofexcessmaternalweightanddepressionreferences2015lutsiv</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>pregnancy complications associated with the co-prevalence of excess maternal weight and depression. [references]</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Lutsiv, O;McKinney, B;Foster, G;Taylor, V., H;Pullenayegum, E;McDonald, S., D</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Objectives: Obesity and depression have become prevalent pregnancy complications, individually associated with adverse perinatal health outcomes. Despite the co-prevalence of these two risk factors, their combined effects on maternal health are yet to be studied. The objective of this study was to examine the combined associations of overweight/obesity and depression with maternal and delivery complications. Methods: A retrospective cohort study of women with singleton gestations at &gt; 20 weeks, in Ontario, Canada (April 2007 to March 2010), was conducted. Our primary outcomes were a composite of maternal complications (for example, gestational hypertension, pre-eclampsia, preterm premature rupture of membranes and so on), and a composite of delivery complications (for example, caesarean delivery, shoulder dystocia, postpartum haemorrhage and so on). Results: The study population consisted of 70 605 women, of whom 50.3% were overweight/obese. Depression was reported in 5.0% of normal-weight women and 6.2% of overweight/obese women. The proportion of women with maternal complications was the highest among the overweight/obese depressed pregnant women (16% of normal-weight non-depressed, 22% of normal-weight depressed, 22% of overweight/obese non-depressed and 29% of overweight/obese depressed, P &lt; 0.001), as was the proportion of women with delivery complications (44%, 49%, 50% and 53%, respectively, P &lt; 0.001). Overweight/obese depressed pregnant women also experienced the highest odds of the composite of maternal complications and the composite of delivery complications (adjusted odds ratio (OR): 1.55, 95% confidence interval (CI): 1.35-1.77 and OR: 1.27, 95% CI: 1.13-1.42, respectively) after adjustment for potential confounders. Conclusions: The combined associations of excess weight and depression with adverse pregnancy outcomes are important to recognize in order to focus counselling and care, both before and during pregnancy. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>International Journal of Obesity</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>10.1038/ijo.2015.119</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>objectiveobeityanddepreionhavebecomeprevalentpregnancycomplication,individuallyaociatedwithadvereperinatalhealthoutcome.depitethecoprevalenceoftheetworikfactor,theircombinedeffectonmaternalhealthareyettobetudied.theobjectiveofthitudywatoexaminethecombinedaociationofoverweight/obeityanddepreionwithmaternalanddeliverycomplication.methodaretropectivecohorttudyofwomenwithingletongetationat&gt;20week,inontario,canada(april2007tomarch2010),waconducted.ourprimaryoutcomewereacompoiteofmaternalcomplication(forexample,getationalhypertenion,preeclampia,pretermprematureruptureofmembraneandoon),andacompoiteofdeliverycomplication(forexample,caeareandelivery,houlderdytocia,potpartumhaemorrhageandoon).reultthetudypopulationconitedof70605women,ofwhom50.3%wereoverweight/obee.depreionwareportedin5.0%ofnormalweightwomenand6.2%ofoverweight/obeewomen.theproportionofwomenwithmaternalcomplicationwathehighetamongtheoverweight/obeedepreedpregnantwomen(16%ofnormalweightnondepreed,22%ofnormalweightdepreed,22%ofoverweight/obeenondepreedand29%ofoverweight/obeedepreed,p&lt;0.001),awatheproportionofwomenwithdeliverycomplication(44%,49%,50%and53%,repectively,p&lt;0.001).overweight/obeedepreedpregnantwomenaloexperiencedthehighetoddofthecompoiteofmaternalcomplicationandthecompoiteofdeliverycomplication(adjutedoddratio(or)1.55,95%confidenceinterval(ci)1.351.77andor1.27,95%ci1.131.42,repectively)afteradjutmentforpotentialconfounder.concluionthecombinedaociationofexceweightanddepreionwithadverepregnancyoutcomeareimportanttorecognizeinordertofocucounellingandcare,bothbeforeandduringpregnancy.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>Lutsiv</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>19417</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>consultationaboutsexualhealthissuesintheyearafterchildbirthacohortstudyreferences2015mcdonald</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>consultation about sexual health issues in the year after childbirth: a cohort study. [references]</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>McDonald, Ellie;Woolhouse, Hannah;Brown, Stephanie, J</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Background: Postnatal sexual health remains underresearched. The main aims of this study were to investigate the prevalence of postnatal sexual health issues, and the extent to which primary care practitioners routinely inquire about sexual health issues. Method: 1,507 first time mothers were recruited in early pregnancy and followed up at 3, 6, and 12 months postpartum. Sexual health issues were assessed at every follow-up using a checklist. Results: Eighty-nine percent of women reported sexual health issues in the first 3 months postpartum. The most common sexual health issues at 3 months postpartum were: loss of interest in sex, pain during sex, vaginal tightness, and lack of lubrication. Fifty-one percent continued to report loss of interest in sex at 12 months postpartum, and around 30 percent reported persisting pain. Although most women had contact with primary care practitioners during the first 3 months postpartum, only 24 percent recalled being asked about sexual health issues by general practitioners and 14 percent by maternal and child health nurses. Women who had a cesarean delivery had equivalent or higher odds of reporting persisting sexual health issues, but had lower odds of being asked directly about sexual problems (OR 0.58 [95% CI 0.4-0.9]). Conclusions: Sexual health issues are extremely common after childbirth. There was no evidence that women who had a cesarean delivery experienced fewer sexual health problems. Despite frequent contact with health professionals, women rarely discussed sexual health issues unless health professionals asked them directly. Given the high prevalence of postpartum sexual health issues routine inquiry is warranted. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Birth: Issues in Perinatal Care</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>10.1111/birt.12193</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>backgroundpotnatalexualhealthremainunderreearched.themainaimofthitudyweretoinvetigatetheprevalenceofpotnatalexualhealthiue,andtheextenttowhichprimarycarepractitionerroutinelyinquireaboutexualhealthiue.method1,507firttimemotherwererecruitedinearlypregnancyandfollowedupat3,6,and12monthpotpartum.exualhealthiuewereaeedateveryfollowupuingachecklit.reulteightyninepercentofwomenreportedexualhealthiueinthefirt3monthpotpartum.themotcommonexualhealthiueat3monthpotpartumwereloofinteretinex,painduringex,vaginaltightne,andlackoflubrication.fiftyonepercentcontinuedtoreportloofinteretinexat12monthpotpartum,andaround30percentreportedperitingpain.althoughmotwomenhadcontactwithprimarycarepractitionerduringthefirt3monthpotpartum,only24percentrecalledbeingakedaboutexualhealthiuebygeneralpractitionerand14percentbymaternalandchildhealthnure.womenwhohadaceareandeliveryhadequivalentorhigheroddofreportingperitingexualhealthiue,buthadloweroddofbeingakeddirectlyaboutexualproblem(or0.58[95%ci0.40.9]).concluionexualhealthiueareextremelycommonafterchildbirth.therewanoevidencethatwomenwhohadaceareandeliveryexperiencedfewerexualhealthproblem.depitefrequentcontactwithhealthprofeional,womenrarelydicuedexualhealthiueunlehealthprofeionalakedthemdirectly.giventhehighprevalenceofpotpartumexualhealthiueroutineinquiryiwarranted.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>McDonald</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q114" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>19418</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>costeffectivenessanalysisoflatentversusactivelaborhospitaladmissionformedicallylowrisktermwomenreferences2015tilden</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>cost-effectiveness analysis of latent versus active labor hospital admission for medically low-risk, term women. [references]</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Tilden, Ellen, L;Lee, Vanessa, R;Allen, Allison, J;Griffin, Emily, E;Caughey, Aaron, B</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Objective: To assess the outcomes and costs of hospital admission during the latent versus active phase of labor. Latent labor hospital admission has been consistently associated with elevated maternal risk for increased interventions, including epidural anesthesia and cesarean delivery, longer hospital stay, and higher utilization of hospital resources. Methods: A cost-effectiveness model was built to simulate a theoretic cohort of 3.2 million term, medically low-risk women either being admitted in latent labor (&lt; 4 cm dilation) or delaying admission until active labor (&gt;= 4 cm dilation). Outcomes included epidural use, mode of delivery, stillbirth, maternal death, and costs of care. All probability, cost, and utility estimates were derived from the literature, and total quality-adjusted life years were calculated. Sensitivity analyses and a Monte Carlo simulation were used to investigate the robustness of model assumptions. Results: Delaying admission until active labor would result in 672,000 fewer epidurals, 67,232 fewer cesarean deliveries, and 9.6 fewer maternal deaths in our theoretic cohort as compared to admission during latent labor. Additionally, delaying admission results in a cost savings of $694 million annually in the United States. Sensitivity analyses indicated the model was robust within a wide range of probabilities and costs. Monte Carlo simulation found that delayed admission was the optimal strategy in 76.79 percent of trials. Conclusion: Delaying admission until active labor is a dominant strategy, resulting in both better outcomes and lower costs. Issues related to clinical translation of these findings are explored. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Birth: Issues in Perinatal Care</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>10.1111/birt.12179</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>objectivetoaetheoutcomeandcotofhopitaladmiionduringthelatentveruactivephaeoflabor.latentlaborhopitaladmiionhabeenconitentlyaociatedwithelevatedmaternalrikforincreaedintervention,includingepiduralanetheiaandceareandelivery,longerhopitaltay,andhigherutilizationofhopitalreource.methodacoteffectivenemodelwabuilttoimulateatheoreticcohortof3.2millionterm,medicallylowrikwomeneitherbeingadmittedinlatentlabor(&lt;4cmdilation)ordelayingadmiionuntilactivelabor(&gt;=4cmdilation).outcomeincludedepiduralue,modeofdelivery,tillbirth,maternaldeath,andcotofcare.allprobability,cot,andutilityetimatewerederivedfromtheliterature,andtotalqualityadjutedlifeyearwerecalculated.enitivityanalyeandamontecarloimulationwereuedtoinvetigatetherobutneofmodelaumption.reultdelayingadmiionuntilactivelaborwouldreultin672,000fewerepidural,67,232fewerceareandeliverie,and9.6fewermaternaldeathinourtheoreticcohortacomparedtoadmiionduringlatentlabor.additionally,delayingadmiionreultinacotavingof$694millionannuallyintheunitedtate.enitivityanalyeindicatedthemodelwarobutwithinawiderangeofprobabilitieandcot.montecarloimulationfoundthatdelayedadmiionwatheoptimaltrategyin76.79percentoftrial.concluiondelayingadmiionuntilactivelaboriadominanttrategy,reultinginbothbetteroutcomeandlowercot.iuerelatedtoclinicaltranlationoftheefindingareexplored.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>Tilden</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q115" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>19419</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>riskfactorsforseveresecondarypostpartumhemorrhagesahistoricalcohortstudyreferences2015debostlegrand</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>risk factors for severe secondary postpartum hemorrhages: a historical cohort study. [references]</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Debost-Legrand, Anne;Riviere, Olivier;Dossou, Mathieu;Vendittelli, Francoise</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Background: The predictive factors of secondary postpartum hemorrhage (PPH) are little known. Our principal objective was to determine if immediate PPH is a risk factor for severe secondary PPH. We also sought to identify other factors associated with severe secondary PPH. Methods: Our historical cohort study included all women who gave birth (&gt;= 22 weeks) in our level III hospital from 2004 through 2013. The hospital discharge database enabled us to identify all women readmitted during the 42-day postpartum period or who underwent a surgical, medical, or interventional radiology procedure during their immediate postpartum hospitalization. We then examined all medical records to identify the cases involving severe secondary PPH. We studied the known risk factors of secondary PPH and assessed other potential ones: maternal age, multiple pregnancy, induction of labor, cesarean birth, preterm birth, and stillbirth. Results: The study included 63 women with a severe secondary PPH and 25,696 women without a secondary PPH. Immediate PPH (aOR 2.7 [95% CI 1.3-5.6]) and maternal age &gt;= 35 years (aOR 2.0 [95% CI 1.1-3.7]) were the only factors associated with severe secondary PPH. Discussion: This cohort study confirms that immediate PPH is a risk factor for severe secondary PPH and reports for the first time an association between secondary PPH and advanced maternal age. It is likely that risk factors for immediate PPH are also risk factors for severe secondary PPH and thus that immediate PPH may be an intermediate factor between its own known risk factors and secondary PPH. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Birth: Issues in Perinatal Care</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>10.1111/birt.12175</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>backgroundthepredictivefactorofecondarypotpartumhemorrhage(pph)arelittleknown.ourprincipalobjectivewatodetermineifimmediatepphiarikfactorforevereecondarypph.wealooughttoidentifyotherfactoraociatedwithevereecondarypph.methodourhitoricalcohorttudyincludedallwomenwhogavebirth(&gt;=22week)inourleveliiihopitalfrom2004through2013.thehopitaldichargedatabaeenabledutoidentifyallwomenreadmittedduringthe42daypotpartumperiodorwhounderwentaurgical,medical,orinterventionalradiologyprocedureduringtheirimmediatepotpartumhopitalization.wethenexaminedallmedicalrecordtoidentifythecaeinvolvingevereecondarypph.wetudiedtheknownrikfactorofecondarypphandaeedotherpotentialonematernalage,multiplepregnancy,inductionoflabor,ceareanbirth,pretermbirth,andtillbirth.reultthetudyincluded63womenwithaevereecondarypphand25,696womenwithoutaecondarypph.immediatepph(aor2.7[95%ci1.35.6])andmaternalage&gt;=35year(aor2.0[95%ci1.13.7])weretheonlyfactoraociatedwithevereecondarypph.dicuionthicohorttudyconfirmthatimmediatepphiarikfactorforevereecondarypphandreportforthefirttimeanaociationbetweenecondarypphandadvancedmaternalage.itilikelythatrikfactorforimmediateppharealorikfactorforevereecondarypphandthuthatimmediatepphmaybeanintermediatefactorbetweenitownknownrikfactorandecondarypph.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Debost-Legrand</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q116" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>19420</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>enhancingmidwivesscopeofpracticeaninnovativeeducationalprogramfordeliverysuiteoperatingroomsreferences2015brown</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>enhancing midwives' scope of practice: an innovative educational program for delivery suite operating rooms. [references]</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Brown, Janie, A;Dunning, Caroline, F;Cavanagh, Debra;Cross, Leonie, A</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Background: This retrospective study examined the enhancement of practice, knowledge, and skill of delivery suite midwives undertaking the circulating and instrument roles during emergent caesarean sections following a tailored educational program implemented to the benchmark standard. Method: All midwives who attended the educational program were invited to participate (N = 48); a total of 20 responses were received. Descriptive data analysis of the bivariate nominal data was performed. Results: Clinically significant outcomes were noted across all theme areas: knowledge of the Australian College of Operating Room Nurses standards, competence and knowledge of the main roles during a caesarean section, knowledge of policies and procedures, and patient safety. An improved working relationship between the perioperative and delivery ward staff also was identified. Conclusion: An educational program for midwives on the instrument and circulating roles for caesarean sections provides the knowledge and skill development required for clinically safe practice. (PsycInfo Database Record (c) 2021 APA, all rights reserved)</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>The Journal of Continuing Education in Nursing</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Journal
-Peer Reviewed Journal</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>10.3928/00220124-20151217-04</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>backgroundthiretropectivetudyexaminedtheenhancementofpractice,knowledge,andkillofdeliveryuitemidwiveundertakingthecirculatingandintrumentroleduringemergentcaeareanectionfollowingatailorededucationalprogramimplementedtothebenchmarktandard.methodallmidwivewhoattendedtheeducationalprogramwereinvitedtoparticipate(n=48)atotalof20reponewerereceived.decriptivedataanalyiofthebivariatenominaldatawaperformed.reultclinicallyignificantoutcomewerenotedacroallthemeareaknowledgeoftheautraliancollegeofoperatingroomnuretandard,competenceandknowledgeofthemainroleduringacaeareanection,knowledgeofpolicieandprocedure,andpatientafety.animprovedworkingrelationhipbetweentheperioperativeanddeliverywardtaffalowaidentified.concluionaneducationalprogramformidwiveontheintrumentandcirculatingroleforcaeareanectionprovidetheknowledgeandkilldevelopmentrequiredforclinicallyafepractice.(pycinfodatabaerecord</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>psycinfo</t>
-        </is>
-      </c>
-      <c r="Q117" t="n">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
